--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_554_New_Zealand.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_554_New_Zealand.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rfc6f80be2aef431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rca895102a9b34604"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R59df34fc045a4ea1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R508d7d9a60e44181"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R10941b7ae5624cc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R078897487c3b4165"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3cd3424f59474c6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Red5e6cc1a89b4935"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rdb8d6e57e4df4300"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc043b73bea544e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R59db5740b91c46a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R64c8d36f1a6f4dd0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ554CommercialTable" displayName="EEZ554CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ554CommercialTable" displayName="EEZ554CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ554FunctionalTable" displayName="EEZ554FunctionalTable" ref="A1:O29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O29"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ554FunctionalTable" displayName="EEZ554FunctionalTable" ref="A1:E29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E29"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ554ValidationTable" displayName="EEZ554ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ554ValidationTable" displayName="EEZ554ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -13893,7 +13847,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f3df730038c4c69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf14bbc5a563e4cc3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13903,20 +13857,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13924,660 +13868,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>213703.92226230883</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.375217064551883</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2372.55923725357</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>213703.92226230883</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2768.44544409917</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$198,A2,'Species'!$U$2:$U$198))</x:f>
-        <x:v>591627649.973212</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.375217064551883</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2372.55923725357</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>507025214.8007596</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>84602435.17245239</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.166860409902292</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.16686040990229198</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>5418.150260170299</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.761709508978954</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>57.77094996426616</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>5418.150260170299</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>91.32074031752292</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$198,A3,'Species'!$U$2:$U$198))</x:f>
-        <x:v>494789.4929103311</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.761709508978954</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>57.77094996426616</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>313011.687579174</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>181777.8053311571</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.580738076386294</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.5807380763862939</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2884.8507522663</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.5729440575305023</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>374.0624013316982</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2884.8507522663</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>374.73689350462655</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$198,A4,'Species'!$U$2:$U$198))</x:f>
-        <x:v>1081060.0091287582</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.5729440575305023</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>374.0624013316982</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1079114.1998762882</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1945.8092524700332</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.001803154154299</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.001803154154299058</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>458.3235384716</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.8410492772395757</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>69.35044900653531</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>458.3235384716</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>69.43020476726936</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$198,A5,'Species'!$U$2:$U$198))</x:f>
-        <x:v>31821.49712574264</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.8410492772395757</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>69.35044900653531</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>31784.943183269523</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>36.553942473117786</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0011500395725847</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0011500395725847481</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>5415.299119196201</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.087356716031526</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.228036208048907</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>5415.299119196201</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.69226162719217</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$198,A6,'Species'!$U$2:$U$198))</x:f>
-        <x:v>68732.3932103415</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.087356716031526</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.228036208048907</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>66218.4737069465</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2513.9195033949945</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0379640206526124</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03796402065261249</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>99978.01348484</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6282992383048587</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>424.91223684054313</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>99978.01348484</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>747.1811931481955</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$198,A7,'Species'!$U$2:$U$198))</x:f>
-        <x:v>74701691.40418912</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6282992383048587</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>424.91223684054313</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>42481881.34471735</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>32219810.05947177</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7584365155117672</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.758436515511767</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>156089.0895450833</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.685753774310017</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>485.0134411082569</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>156089.0895450833</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>584.0880769552317</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$198,A8,'Species'!$U$2:$U$198))</x:f>
-        <x:v>91169776.14608066</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.685753774310017</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>485.0134411082569</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>75705306.4397157</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>15464469.70636496</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.204271938568525</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.20427193856852494</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>58.2650416063</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>251.18864315095797</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>58.2650416063</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>251.18864315095797</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$198,A9,'Species'!$U$2:$U$198))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>14635.516744220611</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>251.18864315095797</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>14635.516744220611</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4995.963434368001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.6826971725470665</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>481.6118593194406</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4995.963434368001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>482.7849073447981</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$198,A10,'Species'!$U$2:$U$198))</x:f>
-        <x:v>2411975.7437593546</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.6826971725470665</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>481.6118593194406</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2406115.238717911</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>5860.505041443743</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0024356709716724</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0024356709716723667</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>36363.6795941058</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.079711227982126</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1201.4652880868923</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>36363.6795941058</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1524.0053595561506</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$198,A11,'Species'!$U$2:$U$198))</x:f>
-        <x:v>55418442.594599865</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.079711227982126</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1201.4652880868923</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>43689698.779431775</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>11728743.81516809</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2684555889108062</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.26845558891080623</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>11268.452254534901</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.360197443292662</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2291.9093866722087</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>11268.452254534901</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2424.989542638764</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$198,A12,'Species'!$U$2:$U$198))</x:f>
-        <x:v>27325878.87897134</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.360197443292662</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2291.9093866722087</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>25826271.49543615</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1499607.3835351877</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0580651908580838</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.05806519085808373</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reee37f82a4234cd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c8084737a81493d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14587,20 +14102,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -14608,1578 +14113,554 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2137.7420699140002</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.097348234114217</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1251.2619383000153</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2137.7420699140002</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1252.0735738457106</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$198,A2,'Species'!$U$2:$U$198))</x:f>
-        <x:v>2676610.3534375494</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.097348234114217</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1251.2619383000153</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2674875.285986079</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1735.0674514705315</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0006486535879116</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0006486535879114484</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>9.8309797592</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4599999999999995</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.4031503126603</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>9.8309797592</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$198,A3,'Species'!$U$2:$U$198))</x:f>
-        <x:v>2835.2855332132813</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4599999999999995</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.4031503126603</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2835.285533213278</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>3.183231456205249e-12</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>1.1227198879675577e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>31208.4355030267</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.226435228468988</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1684.3611991066782</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>31208.4355030267</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1761.6548977525717</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$198,A4,'Species'!$U$2:$U$198))</x:f>
-        <x:v>54978493.25510223</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.226435228468988</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1684.3611991066782</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>52566277.84612148</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2412215.4089807495</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0458890282481497</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0458890282481496</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>130.2513088642</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.130376506066185</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1350.1328558441717</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>130.2513088642</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1532.4664377846543</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$198,A5,'Species'!$U$2:$U$198))</x:f>
-        <x:v>199605.75931190935</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.130376506066185</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1350.1328558441717</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>175856.57161426364</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>23749.187697645713</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1350486221790954</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.13504862217909536</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>39989.967803290296</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.7674077274230604</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>585.3393587118776</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>39989.967803290296</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>867.8214182253043</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$198,A6,'Species'!$U$2:$U$198))</x:f>
-        <x:v>34704150.57383564</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.7674077274230604</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>585.3393587118776</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>23407702.108886573</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>11296448.464949068</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.4825953616634777</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.4825953616634778</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>162576.85610729372</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.459265477157207</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2879.1578593188183</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>162576.85610729372</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>3157.318427070764</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$198,A7,'Species'!$U$2:$U$198))</x:f>
-        <x:v>513306903.60279053</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.459265477157207</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2879.1578593188183</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>468084433.0046593</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>45222470.59813124</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.096611780716239</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.09661178071623906</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.1264752968</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>251.18864315095797</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.1264752968</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>251.18864315095797</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$198,A8,'Species'!$U$2:$U$198))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>31.769158195306698</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>251.18864315095797</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>31.769158195306698</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>11336.3639363688</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.360119194200568</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2291.4964786551445</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>11336.3639363688</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2423.9678087295306</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$198,A9,'Species'!$U$2:$U$198))</x:f>
-        <x:v>27478981.249800358</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.360119194200568</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2291.4964786551445</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>25977238.040942278</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1501743.2088580802</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.057809964496272</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.05780996449627203</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5266.461153001401</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7163716950410146</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>520.4412305282985</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5266.461153001401</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>545.939608572211</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$198,A10,'Species'!$U$2:$U$198))</x:f>
-        <x:v>2875169.7404303397</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7163716950410146</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>520.4412305282985</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2740883.522997531</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>134286.2174328086</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0489937701861727</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.04899377018617276</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>262.5199645181</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>831.7637711026708</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>262.5199645181</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$198,A11,'Species'!$U$2:$U$198))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>218354.59567731418</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.92</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>218354.59567731418</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>27431.050893667296</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.220158137148787</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1660.1913132940786</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>27431.050893667296</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1863.079083947027</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$198,A12,'Species'!$U$2:$U$198))</x:f>
-        <x:v>51106217.17067794</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.220158137148787</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1660.1913132940786</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>45540792.408194214</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>5565424.762483723</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1222074643014408</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.12220746430144086</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>5408.9799006844</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.7618462031303395</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>57.78913622778537</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>5408.9799006844</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>91.36733187020533</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$198,A13,'Species'!$U$2:$U$198))</x:f>
-        <x:v>494204.0616651018</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.7618462031303395</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>57.78913622778537</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>312580.2763340038</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>181623.785331098</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.581046851263981</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.5810468512639811</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>4510.969201284601</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.769536985335621</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>588.2162056094301</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>4510.969201284601</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1197.5573007391863</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$198,A14,'Species'!$U$2:$U$198))</x:f>
-        <x:v>5402144.10040799</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.769536985335621</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>588.2162056094301</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>2653425.187200629</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2748718.9132073605</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.035913477593565</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.0359134775935652</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>24490.492183027105</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.902668075901597</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>799.2231884421834</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>24490.492183027105</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>974.7387008018752</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$198,A15,'Species'!$U$2:$U$198))</x:f>
-        <x:v>23871830.532482322</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.902668075901597</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>799.2231884421834</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>19573369.24903729</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>4298461.28344503</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.219607632633633</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.219607632633633</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>48994.8416149695</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.7155893092741517</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>519.504494572074</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>48994.8416149695</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>619.4992587550222</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$198,A16,'Species'!$U$2:$U$198))</x:f>
-        <x:v>30352268.063293315</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.7155893092741517</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>519.504494572074</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>25453040.429823548</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>4899227.633469768</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.192481037657462</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.19248103765746197</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>87766.2496426471</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.4724918970113214</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>296.8191362963638</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>87766.2496426471</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>468.7652720442235</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$198,A17,'Species'!$U$2:$U$198))</x:f>
-        <x:v>41141769.8900367</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.4724918970113214</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>296.8191362963638</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>26050702.414901562</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>15091067.47513514</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.579295991132382</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.5792959911323821</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>70214.27930557728</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.8083214416040136</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>643.1635765562913</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>70214.27930557728</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>748.4676724554544</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$198,A18,'Species'!$U$2:$U$198))</x:f>
-        <x:v>52553118.2049826</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.8083214416040136</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>643.1635765562913</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>45159267.003497474</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>7393851.201485127</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.1637283262572107</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.16372832625721076</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>156.82062016339998</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.2901216419181556</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>195.0390809914009</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>156.82062016339998</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>458.47964354195784</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$198,A19,'Species'!$U$2:$U$198))</x:f>
-        <x:v>71899.06203254439</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.2901216419181556</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>195.0390809914009</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>30586.149637171085</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>41312.91239537331</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>2.3507065415375488</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>1.3507065415375488</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>7078.0752969407995</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.18630756775183</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>15.35704184892372</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>7078.0752969407995</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>17.296834593622687</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$198,A20,'Species'!$U$2:$U$198))</x:f>
-        <x:v>122428.29765239179</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.18630756775183</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>15.35704184892372</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>108698.29854495304</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>13729.99910743875</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.1263129164966699</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.12631291649666992</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>9.170359485899999</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>2.6810827987037227</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>47.98249190468145</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>9.170359485899999</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>63.83950881417897</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$198,A21,'Species'!$U$2:$U$198))</x:f>
-        <x:v>585.4312452293027</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>2.6810827987037227</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>47.98249190468145</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>440.01669979521546</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>145.41454543408724</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.3304750603823978</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.3304750603823978</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>4.2847021827</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.51</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>323.5936569296281</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>4.2847021827</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$198,A22,'Species'!$U$2:$U$198))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1386.5024481542525</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>1386.5024481542525</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small bathypelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>11.2497428084</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>316.22776601683796</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>11.2497428084</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$198,A23,'Species'!$U$2:$U$198))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>3557.481036564321</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>3557.481036564321</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>188.0407541085</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.15</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>141.2537544622754</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>188.0407541085</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$198,A24,'Species'!$U$2:$U$198))</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>26561.462509743164</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.15</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
-        <x:v>26561.462509743164</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>371.84269897589996</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.1127542044884455</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>129.64453205277582</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>371.84269897589996</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>130.14840558670696</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$198,A25,'Species'!$U$2:$U$198))</x:f>
-        <x:v>48394.734400771216</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.1127542044884455</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>129.64453205277582</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>48207.372705971735</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>187.36169479948148</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.003886577597627</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.0038865775976269262</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>528.2152446889</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>2.8086853302545087</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>64.3702699230629</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>528.2152446889</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>361.34615280385435</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$198,A26,'Species'!$U$2:$U$198))</x:f>
-        <x:v>190868.5465206806</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>2.8086853302545087</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>64.3702699230629</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>34001.35787810122</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>156867.18864257936</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>5.613556588091755</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>4.613556588091755</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
       <x:c r="A27" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B27" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="n">
+      <x:c r="B27" s="31" t="n">
         <x:v>2884.7242769695</x:v>
       </x:c>
+      <x:c r="C27" s="32" t="n">
+        <x:v>3.57295163993662</x:v>
+      </x:c>
+      <x:c r="D27" s="32" t="n">
+        <x:f>IF(C27="","",(1/'Metadata'!$B$5)^(C27-1))</x:f>
+        <x:v>374.0689321947835</x:v>
+      </x:c>
       <x:c r="E27" s="31" t="n">
-        <x:v>2884.7242769695</x:v>
-      </x:c>
-      <x:c r="F27" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="32" t="n">
-        <x:f>IF(E27=0,"",I27/E27)</x:f>
-        <x:v>374.74231024471413</x:v>
-      </x:c>
-      <x:c r="I27" s="31" t="n">
-        <x:f>IF(C27=0,"",SUMIF('Species'!$G$2:$G$198,A27,'Species'!$U$2:$U$198))</x:f>
-        <x:v>1081028.239970563</x:v>
-      </x:c>
-      <x:c r="J27" s="32" t="n">
-        <x:v>3.57295163993662</x:v>
-      </x:c>
-      <x:c r="K27" s="32" t="n">
-        <x:f>IF(J27="","",(1/'Metadata'!$B$5)^(J27-1))</x:f>
-        <x:v>374.0689321947835</x:v>
-      </x:c>
-      <x:c r="L27" s="31" t="n">
-        <x:f>IF(E27=0,"",E27*K27)</x:f>
+        <x:f>IF(B27=0,"",B27*D27)</x:f>
         <x:v>1079085.7299623496</x:v>
-      </x:c>
-      <x:c r="M27" s="31" t="n">
-        <x:f>IF(E27=0,"",I27-L27)</x:f>
-        <x:v>1942.510008213343</x:v>
-      </x:c>
-      <x:c r="N27" s="32" t="n">
-        <x:f>IF(L27=0,"",I27/L27)</x:f>
-        <x:v>1.001800144283514</x:v>
-      </x:c>
-      <x:c r="O27" s="34" t="n">
-        <x:f>IF(L27=0,"",M27/L27)</x:f>
-        <x:v>0.0018001442835140812</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="18" customHeight="1">
       <x:c r="A28" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B28" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C28" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D28" s="31" t="n">
+      <x:c r="B28" s="31" t="n">
         <x:v>3487.4935898946</x:v>
       </x:c>
+      <x:c r="C28" s="32" t="n">
+        <x:v>3.5180960021076935</x:v>
+      </x:c>
+      <x:c r="D28" s="32" t="n">
+        <x:f>IF(C28="","",(1/'Metadata'!$B$5)^(C28-1))</x:f>
+        <x:v>329.68258145412875</x:v>
+      </x:c>
       <x:c r="E28" s="31" t="n">
-        <x:v>3487.4935898946</x:v>
-      </x:c>
-      <x:c r="F28" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G28" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H28" s="32" t="n">
-        <x:f>IF(E28=0,"",I28/E28)</x:f>
-        <x:v>329.72796765877064</x:v>
-      </x:c>
-      <x:c r="I28" s="31" t="n">
-        <x:f>IF(C28=0,"",SUMIF('Species'!$G$2:$G$198,A28,'Species'!$U$2:$U$198))</x:f>
-        <x:v>1149924.1736189367</x:v>
-      </x:c>
-      <x:c r="J28" s="32" t="n">
-        <x:v>3.5180960021076935</x:v>
-      </x:c>
-      <x:c r="K28" s="32" t="n">
-        <x:f>IF(J28="","",(1/'Metadata'!$B$5)^(J28-1))</x:f>
-        <x:v>329.68258145412875</x:v>
-      </x:c>
-      <x:c r="L28" s="31" t="n">
-        <x:f>IF(E28=0,"",E28*K28)</x:f>
+        <x:f>IF(B28=0,"",B28*D28)</x:f>
         <x:v>1149765.8895211783</x:v>
-      </x:c>
-      <x:c r="M28" s="31" t="n">
-        <x:f>IF(E28=0,"",I28-L28)</x:f>
-        <x:v>158.28409775835462</x:v>
-      </x:c>
-      <x:c r="N28" s="32" t="n">
-        <x:f>IF(L28=0,"",I28/L28)</x:f>
-        <x:v>1.000137666371216</x:v>
-      </x:c>
-      <x:c r="O28" s="34" t="n">
-        <x:f>IF(L28=0,"",M28/L28)</x:f>
-        <x:v>0.00013766637121603273</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="18" customHeight="1">
       <x:c r="A29" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B29" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C29" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D29" s="31" t="n">
+      <x:c r="B29" s="31" t="n">
         <x:v>178.6739575425</x:v>
       </x:c>
+      <x:c r="C29" s="32" t="n">
+        <x:v>4.189054093993917</x:v>
+      </x:c>
+      <x:c r="D29" s="32" t="n">
+        <x:f>IF(C29="","",(1/'Metadata'!$B$5)^(C29-1))</x:f>
+        <x:v>1545.4469222746864</x:v>
+      </x:c>
       <x:c r="E29" s="31" t="n">
-        <x:v>178.6739575425</x:v>
-      </x:c>
-      <x:c r="F29" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H29" s="32" t="n">
-        <x:f>IF(E29=0,"",I29/E29)</x:f>
-        <x:v>1607.0137686649323</x:v>
-      </x:c>
-      <x:c r="I29" s="31" t="n">
-        <x:f>IF(C29=0,"",SUMIF('Species'!$G$2:$G$198,A29,'Species'!$U$2:$U$198))</x:f>
-        <x:v>287131.509872651</x:v>
-      </x:c>
-      <x:c r="J29" s="32" t="n">
-        <x:v>4.189054093993917</x:v>
-      </x:c>
-      <x:c r="K29" s="32" t="n">
-        <x:f>IF(J29="","",(1/'Metadata'!$B$5)^(J29-1))</x:f>
-        <x:v>1545.4469222746864</x:v>
-      </x:c>
-      <x:c r="L29" s="31" t="n">
-        <x:f>IF(E29=0,"",E29*K29)</x:f>
+        <x:f>IF(B29=0,"",B29*D29)</x:f>
         <x:v>276131.11777469463</x:v>
       </x:c>
-      <x:c r="M29" s="31" t="n">
-        <x:f>IF(E29=0,"",I29-L29)</x:f>
-        <x:v>11000.392097956385</x:v>
-      </x:c>
-      <x:c r="N29" s="32" t="n">
-        <x:f>IF(L29=0,"",I29/L29)</x:f>
-        <x:v>1.039837567698299</x:v>
-      </x:c>
-      <x:c r="O29" s="34" t="n">
-        <x:f>IF(L29=0,"",M29/L29)</x:f>
-        <x:v>0.03983756769829905</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G29">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O29">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R588fae95626e4d1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R923e68f3346446ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16354,7 +14835,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -16453,7 +14934,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>844346453.6499318</x:v>
+        <x:v>698639252.9198685</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16467,7 +14948,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>844346453.6499316</x:v>
+        <x:v>743350086.3792835</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16481,7 +14962,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>2.384185791015625e-7</x:v>
+        <x:v>-145707200.73006308</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16495,7 +14976,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-100996367.270648</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16506,9 +14987,9 @@
         <x:v>EEZ_554</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -16520,47 +15001,19 @@
         <x:v>EEZ_554</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_554</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_554</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02cb8afb24684586"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R492b32ef8344469a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16607,7 +15060,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
